--- a/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Syracuse_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Syracuse_20251031.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,39 +500,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2536555</t>
+          <t>1589290</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bacon (Pre-Cooked)</t>
+          <t>Sausage - Patty (1.5oz)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>359.50</t>
+          <t>77.25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1589290</t>
+          <t>7226918</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sausage - Patty (1.5oz)</t>
+          <t>Mozz (Sliced)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -542,24 +542,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.25</t>
+          <t>88.65</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7226918</t>
+          <t>9035601</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mozz (Sliced)</t>
+          <t>American Cheese (Sliced)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -569,78 +569,78 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>44.90</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>134.70</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9035601</t>
+          <t>6297594</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Cheese (Sliced)</t>
+          <t>Avocado - Halves Fresh</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.90</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>134.70</t>
+          <t>71.50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2393502</t>
+          <t>4617771</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>English Muffin</t>
+          <t>Egg Patty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30.79</t>
+          <t>188.32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6297594</t>
+          <t>0017354</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Avocado - Halves Fresh</t>
+          <t>Hash Brown</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -650,118 +650,64 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>71.50</t>
+          <t>47.78</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4617771</t>
+          <t>2240376</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Egg Patty</t>
+          <t>Chobani - Vanilla</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>188.32</t>
+          <t>15.39</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0017354</t>
+          <t>7937269</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hash Brown</t>
+          <t>Chobani - Peach</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>47.78</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2240376</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Chobani - Vanilla</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>7937269</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Chobani - Peach</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
         <is>
           <t>15.39</t>
         </is>
